--- a/LubanConfig/Moba/Production/Datas/J-战斗场景表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-战斗场景表.xlsx
@@ -10,6 +10,7 @@
     <sheet name="战斗地图" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="战斗开局" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="玩法" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="副本" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'战斗地图'!$A$3:$AB$9</definedName>
@@ -2145,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2192,15 +2193,10 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>WinPolicy</t>
+          <t>OmittedFields</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>OmittedFields</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>NullFields</t>
         </is>
@@ -2239,15 +2235,10 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2286,15 +2277,10 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>胜利策略；用于玩法配置。</t>
+          <t>迁移兼容字段：逗号分隔的原 JSON 缺失字段名；新数据通常留空。</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>迁移兼容字段：逗号分隔的原 JSON 缺失字段名；新数据通常留空。</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>迁移兼容字段：逗号分隔的原 JSON 显式 null 字段名；新数据通常留空。</t>
         </is>
@@ -2319,11 +2305,439 @@
           <t>900001,900002,900003,900004</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>GameplayId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>FlowProfileId</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>MinPlayerCount</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MaxPlayerCount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AllowedHostModes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SceneProviderId</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GameplayHandlerId</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>OutcomeRuleId</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>RequiredPortGroups</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>OmittedFields</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NullFields</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>副本 ID，客户端副本目录的唯一标识。</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>副本名称，用于大厅展示。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>玩法 ID，关联 gameplays；副本只引用，不复制玩法常量。</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>战斗流程 Profile ID，对应 battle_flow_profiles.json；客户端装配的核心。</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>入场协议约束：最少玩家数。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>入场协议约束：最多玩家数，0 表示不限。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>允许的宿主模式；空表示不限制：Local/GatewayRemote。</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>场景装配器 ID，对应 IBattleSceneProvider 注册。</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>玩法处理器 ID，对应 IDungeonGameplayHandler 注册。</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>胜负规则 ID，对应 IBattleOutcomeRule 注册。</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>副本需要的 Feature 端口组；空表示不需要额外端口。</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>玩法签名标签；由玩法表主导，通过 Tags 组归并。</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>迁移字段，写入值时 JSON 将跳过该字段。</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>迁移字段，写入值时 JSON 输出为 null 的字段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Standard Local Battle</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>moba.standard</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>unity_map</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>team_deathmatch</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>team_deathmatch</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>deathmatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Remote Ranked Deathmatch</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>moba.standard</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Local,GatewayRemote</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>unity_map</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>team_deathmatch</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>team_deathmatch</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>deathmatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Headless Replay Verification</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>moba.quiet</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>team_deathmatch</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>team_deathmatch</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>deathmatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Trigger-Driven Scenario</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>moba.quiet</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>triggers_only</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>triggers_authoritative</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LubanConfig/Moba/Production/Datas/J-战斗场景表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-战斗场景表.xlsx
@@ -2146,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2173,30 +2173,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>MapId</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>DefaultDurationMs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TriggerIds</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FeatureIds</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OmittedFields</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>NullFields</t>
         </is>
@@ -2220,25 +2230,35 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>(list#sep=,),int</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>(list#sep=,),int</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>(list#sep=,),string</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2257,30 +2277,40 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>默认持续时间，单位毫秒。</t>
+          <t>地图 ID，引用 battle_maps。</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>默认对局时长，单位毫秒；0 表示从 0 递增且不限时，正值表示倒计时。</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
           <t>编辑器和调试时显示的名称。</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>暂不使用；单位身份与玩法类型由专用字段表示，不通过旧数字标签配置。</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>触发器 ID 列表；由 Trigger Authoring 发布，逗号分隔。</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>?????? ID??????????????????????????????</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>迁移兼容字段：逗号分隔的原 JSON 缺失字段名；新数据通常留空。</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>迁移兼容字段：逗号分隔的原 JSON 显式 null 字段名；新数据通常留空。</t>
         </is>
@@ -2292,21 +2322,59 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Default Count-up Gameplay</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>900002,900003,900004</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>minion_waves,structures</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>600000</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Default Battle Gameplay</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10-Minute Timed Gameplay</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>900001,900002,900003,900004</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>minion_waves,structures</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2319,7 +2387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2739,6 +2807,50 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10-Minute Timed Battle</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>moba.standard</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>unity_map</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>team_deathmatch</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>team_deathmatch</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>deathmatch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LubanConfig/Moba/Production/Datas/J-战斗场景表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-战斗场景表.xlsx
@@ -2335,7 +2335,7 @@
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>900002,900003,900004</t>
+          <t>900002,900003,900004,900005,900006</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>900001,900002,900003,900004</t>
+          <t>900001,900002,900003,900004,900005,900006</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
